--- a/ZR.WinFormsApp/res/太仓申通网点质控日报-模板.xlsx
+++ b/ZR.WinFormsApp/res/太仓申通网点质控日报-模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kai\Zr.Admin.NET\ZR.WinFormsApp\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ms363\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE90B1B-35A7-47BC-A31C-C132230DEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43BE5017-C5D0-442B-89C8-28A0D3C2EAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C1AF3C2E-6E60-4347-8FF7-A3CE6D1F1A04}"/>
   </bookViews>
   <sheets>
     <sheet name="质控数据" sheetId="1" r:id="rId1"/>
@@ -50,10 +50,9 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>江苏太仓市</t>
     </r>
@@ -61,10 +60,9 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FFFF0000"/>
+        <color indexed="10"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>KPI考核</t>
     </r>
@@ -72,10 +70,9 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>说明：
 1、</t>
@@ -86,7 +83,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>健康分占比45%，得分上线45分：90-100分按星级得分*0.45，80-90分按星级得分*0.35，70-80分按星级得分*0.25，60-70分按星级得分*0.2，50-60分按星级得分*0.1，低于50分不得分。
 2、进港投诉占比25%，得分上线25分：万10以内开始得分，每低于万0.1加0.5分，万5以内得25分。
@@ -197,10 +193,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>网点出仓率</t>
     </r>
@@ -208,10 +203,9 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（88%）</t>
     </r>
@@ -219,10 +213,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-1）</t>
@@ -233,10 +226,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>交货滞留率</t>
     </r>
@@ -244,10 +236,9 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（2.8%）</t>
     </r>
@@ -255,10 +246,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-1）</t>
@@ -269,10 +259,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>进港投诉率</t>
     </r>
@@ -280,10 +269,9 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（百万分之400）</t>
     </r>
@@ -291,10 +279,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-2）</t>
@@ -305,10 +292,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">虚假签收
 </t>
@@ -317,10 +303,9 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（百万分之300）</t>
     </r>
@@ -328,10 +313,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-2）</t>
@@ -344,7 +328,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>送货上门签收率</t>
     </r>
@@ -354,7 +337,6 @@
         <sz val="10"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（97%）</t>
     </r>
@@ -364,7 +346,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-2）</t>
@@ -410,10 +391,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>当天揽收率</t>
     </r>
@@ -421,10 +401,9 @@
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（98%）</t>
     </r>
@@ -432,10 +411,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-2）</t>
@@ -456,7 +434,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>客户声音</t>
     </r>
@@ -466,7 +443,6 @@
         <sz val="10"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t>（95%）</t>
     </r>
@@ -476,7 +452,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 （T-2）</t>
@@ -1488,11 +1463,11 @@
   </si>
   <si>
     <t>未及时出仓量</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>{{Name}}</t>
-    <phoneticPr fontId="21" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1505,7 +1480,7 @@
     <numFmt numFmtId="178" formatCode="0.0_ "/>
     <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1518,15 +1493,59 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1553,15 +1572,15 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1585,14 +1604,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1628,6 +1639,14 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
@@ -1636,53 +1655,9 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1702,19 +1677,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEE822F"/>
+        <fgColor rgb="FFBFBFBF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1738,7 +1707,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBFBFBF"/>
+        <fgColor rgb="FFEE822F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1753,29 +1728,51 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1783,33 +1780,11 @@
       <left/>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1854,56 +1829,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1921,13 +1846,63 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1947,40 +1922,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1989,283 +1964,283 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2274,112 +2249,112 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2579,7 +2554,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{DDE44D78-C522-49AF-B769-1CA1B1C57C8D}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -2588,7 +2563,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{0E982EEB-209B-4E44-B8F5-EB65B7453E72}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -2601,12 +2576,6 @@
       <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF0000"/>
-      <color rgb="FFFFFF00"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2875,7 +2844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37110827-E2B6-409C-A634-C0563AF43C42}">
   <dimension ref="A1:T37"/>
   <sheetFormatPr defaultColWidth="21" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2903,21 +2872,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="31" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
       <c r="N1" s="95"/>
       <c r="O1" s="95"/>
     </row>
@@ -2982,7 +2951,6 @@
       <c r="K3" s="97"/>
       <c r="L3" s="43"/>
       <c r="M3" s="5">
-        <f t="shared" ref="M3:M6" si="0">D3+F3+H3+J3+L3</f>
         <v>0</v>
       </c>
       <c r="N3" s="48"/>
@@ -3006,7 +2974,6 @@
       <c r="K4" s="97"/>
       <c r="L4" s="43"/>
       <c r="M4" s="5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N4" s="48"/>
@@ -3030,7 +2997,6 @@
       <c r="K5" s="97"/>
       <c r="L5" s="43"/>
       <c r="M5" s="5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N5" s="48"/>
@@ -3054,7 +3020,6 @@
       <c r="K6" s="97"/>
       <c r="L6" s="43"/>
       <c r="M6" s="5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N6" s="48"/>
@@ -3136,7 +3101,6 @@
         <v>10</v>
       </c>
       <c r="C9" s="49">
-        <f t="shared" ref="C9:C12" si="1">SUM(E9:O9)</f>
         <v>0</v>
       </c>
       <c r="D9" s="50"/>
@@ -3161,7 +3125,6 @@
         <v>11</v>
       </c>
       <c r="C10" s="49">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D10" s="50"/>
@@ -3186,7 +3149,6 @@
         <v>12</v>
       </c>
       <c r="C11" s="49">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D11" s="50"/>
@@ -3211,7 +3173,6 @@
         <v>13</v>
       </c>
       <c r="C12" s="49">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D12" s="50"/>
@@ -3249,56 +3210,56 @@
     <row r="14" spans="1:17" s="37" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54"/>
       <c r="B14" s="54"/>
-      <c r="C14" s="141">
+      <c r="C14" s="122">
         <v>20260120</v>
       </c>
-      <c r="D14" s="141"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="129">
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="123">
         <v>20260120</v>
       </c>
-      <c r="G14" s="129"/>
-      <c r="H14" s="130">
+      <c r="G14" s="123"/>
+      <c r="H14" s="124">
         <v>20260119</v>
       </c>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130">
+      <c r="I14" s="124"/>
+      <c r="J14" s="124">
         <v>20260119</v>
       </c>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130">
+      <c r="K14" s="124"/>
+      <c r="L14" s="124">
         <v>20260119</v>
       </c>
-      <c r="M14" s="130"/>
+      <c r="M14" s="124"/>
       <c r="P14" s="54"/>
       <c r="Q14" s="117"/>
     </row>
     <row r="15" spans="1:17" s="37" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="131" t="s">
+      <c r="A15" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="132" t="s">
+      <c r="B15" s="125"/>
+      <c r="C15" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="134" t="s">
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="125"/>
-      <c r="H15" s="135" t="s">
+      <c r="G15" s="129"/>
+      <c r="H15" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="136"/>
-      <c r="J15" s="137" t="s">
+      <c r="I15" s="131"/>
+      <c r="J15" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="K15" s="138"/>
-      <c r="L15" s="126" t="s">
+      <c r="K15" s="133"/>
+      <c r="L15" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="127"/>
+      <c r="M15" s="135"/>
       <c r="P15" s="54"/>
       <c r="Q15" s="117"/>
     </row>
@@ -3471,23 +3432,23 @@
     <row r="22" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="73"/>
       <c r="B22" s="73"/>
-      <c r="C22" s="128">
+      <c r="C22" s="136">
         <v>20260119</v>
       </c>
-      <c r="D22" s="128"/>
-      <c r="E22" s="129">
+      <c r="D22" s="136"/>
+      <c r="E22" s="123">
         <v>20260120</v>
       </c>
-      <c r="F22" s="129"/>
-      <c r="G22" s="129"/>
-      <c r="H22" s="129">
+      <c r="F22" s="123"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="123">
         <v>20260119</v>
       </c>
-      <c r="I22" s="129"/>
-      <c r="J22" s="130">
+      <c r="I22" s="123"/>
+      <c r="J22" s="124">
         <v>20260119</v>
       </c>
-      <c r="K22" s="130"/>
+      <c r="K22" s="124"/>
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
@@ -3495,27 +3456,27 @@
       <c r="P22"/>
     </row>
     <row r="23" spans="1:20" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="121"/>
-      <c r="C23" s="123" t="s">
+      <c r="B23" s="138"/>
+      <c r="C23" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="123"/>
-      <c r="E23" s="124" t="s">
+      <c r="D23" s="140"/>
+      <c r="E23" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="124"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="124" t="s">
+      <c r="F23" s="141"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="125"/>
-      <c r="J23" s="126" t="s">
+      <c r="I23" s="129"/>
+      <c r="J23" s="134" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="126"/>
+      <c r="K23" s="134"/>
       <c r="P23" s="111"/>
       <c r="Q23" s="115"/>
       <c r="R23" s="115"/>
@@ -3680,26 +3641,26 @@
       <c r="S29" s="116"/>
     </row>
     <row r="30" spans="1:20" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="120" t="s">
+      <c r="A30" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="121"/>
-      <c r="C30" s="122" t="s">
+      <c r="B30" s="138"/>
+      <c r="C30" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="122" t="s">
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="G30" s="122"/>
-      <c r="H30" s="122"/>
-      <c r="I30" s="122" t="s">
+      <c r="G30" s="139"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="139" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="122"/>
-      <c r="K30" s="122"/>
-      <c r="L30" s="122"/>
+      <c r="J30" s="139"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="139"/>
     </row>
     <row r="31" spans="1:20" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="74" t="s">
@@ -3840,22 +3801,10 @@
       <c r="P37"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AT47">
-    <sortCondition ref="C2:C47"/>
-  </sortState>
   <mergeCells count="25">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="H22:I22"/>
@@ -3866,21 +3815,27 @@
     <mergeCell ref="I30:L30"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <ignoredErrors>
-    <ignoredError sqref="C9:C12" formulaRange="1"/>
-  </ignoredErrors>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D249E5A6-BC87-45C6-ABDF-53CEF4688FD6}">
   <dimension ref="B2:J107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5463,13 +5418,13 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06AE447D-887C-4A87-B94B-467A45581A1C}">
   <dimension ref="A2:O75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6775,14 +6730,14 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{616E5222-DA76-45F6-B609-51BB7CBA7AF6}">
   <dimension ref="B1:P65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8197,14 +8152,14 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="B25:M25"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E6F706-5085-4899-A12B-B162333FC299}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8432,14 +8387,14 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B1:XCT47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1665B3DE-7108-45FD-891E-4143B0128E7B}">
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -8447,7 +8402,7 @@
     <col min="3" max="3" width="20.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" customWidth="1"/>
     <col min="5" max="5" width="23.109375" style="1" customWidth="1"/>
-    <col min="6" max="16322" width="9" style="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8886,7 +8841,7 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B25:F25"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
